--- a/Assets/Resources/MasterData/ActionEffectData.xlsx
+++ b/Assets/Resources/MasterData/ActionEffectData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017549F4-3C67-42E2-9F74-EAFF04A702A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AB25A6-9122-4673-AD2B-DD94691C8A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="-15030" windowWidth="10095" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1035" yWindow="-15150" windowWidth="20790" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionEffectData" sheetId="1" r:id="rId1"/>
@@ -532,13 +532,13 @@
       </c>
       <c r="B6" s="2">
         <f>VLOOKUP(C6,reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6" s="2">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>

--- a/Assets/Resources/MasterData/ActionEffectData.xlsx
+++ b/Assets/Resources/MasterData/ActionEffectData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AB25A6-9122-4673-AD2B-DD94691C8A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E3DACA-FAAD-4EFF-941E-0A3FF0EF4F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1035" yWindow="-15150" windowWidth="20790" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9990" yWindow="-15615" windowWidth="18030" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionEffectData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -79,6 +79,13 @@
     </rPh>
     <rPh sb="4" eb="9">
       <t>マンプクドカイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>固定ダメージ</t>
+    <rPh sb="0" eb="2">
+      <t>コテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -428,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
@@ -541,6 +548,24 @@
         <v>5000</v>
       </c>
       <c r="E6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <f>VLOOKUP(C7,reference!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -555,7 +580,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C6</xm:sqref>
+          <xm:sqref>C2:C7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -565,7 +590,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ADDE4F9-58C1-4B40-8230-606D1EA7C219}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="21.125" bestFit="1" customWidth="1"/>
@@ -595,8 +620,17 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/Resources/MasterData/ActionEffectData.xlsx
+++ b/Assets/Resources/MasterData/ActionEffectData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E3DACA-FAAD-4EFF-941E-0A3FF0EF4F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80B8DA0-8566-409E-A1F7-76010A9A1006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9990" yWindow="-15615" windowWidth="18030" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16710" yWindow="3675" windowWidth="8685" windowHeight="4350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionEffectData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="9">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -86,6 +86,13 @@
     <t>固定ダメージ</t>
     <rPh sb="0" eb="2">
       <t>コテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムを焼く</t>
+    <rPh sb="5" eb="6">
+      <t>ヤ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -435,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
@@ -566,6 +573,96 @@
         <v>20</v>
       </c>
       <c r="E7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <f>VLOOKUP(C8,reference!A:B,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <f>VLOOKUP(C9,reference!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2">
+        <v>50</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <f>VLOOKUP(C10,reference!A:B,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <f>VLOOKUP(C11,reference!A:B,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <f>VLOOKUP(C12,reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2">
         <v>0</v>
       </c>
     </row>
@@ -580,7 +677,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C7</xm:sqref>
+          <xm:sqref>C2:C12</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -590,7 +687,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ADDE4F9-58C1-4B40-8230-606D1EA7C219}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="21.125" bestFit="1" customWidth="1"/>
@@ -628,6 +725,14 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/MasterData/ActionEffectData.xlsx
+++ b/Assets/Resources/MasterData/ActionEffectData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80B8DA0-8566-409E-A1F7-76010A9A1006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C19BDCF-548A-4FB1-9EBA-DD0F82AC5069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16710" yWindow="3675" windowWidth="8685" windowHeight="4350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="435" yWindow="-9480" windowWidth="16530" windowHeight="4350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionEffectData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="10">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -93,6 +93,13 @@
     <t>アイテムを焼く</t>
     <rPh sb="5" eb="6">
       <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムを腐らせる</t>
+    <rPh sb="5" eb="6">
+      <t>クサ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -442,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
@@ -663,6 +670,24 @@
         <v>5</v>
       </c>
       <c r="E12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <f>VLOOKUP(C13,reference!A:B,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
         <v>0</v>
       </c>
     </row>
@@ -677,7 +702,7 @@
           <x14:formula1>
             <xm:f>reference!$A:$A</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C12</xm:sqref>
+          <xm:sqref>C2:C13</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -687,7 +712,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ADDE4F9-58C1-4B40-8230-606D1EA7C219}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="21.125" bestFit="1" customWidth="1"/>
@@ -733,6 +758,14 @@
         <v>4</v>
       </c>
     </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
